--- a/docs/DB设计书.xlsx
+++ b/docs/DB设计书.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage-backend\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39ACD27-BE05-4791-A29B-4A329D3A2E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028634F7-0478-4AB6-B2BA-4FF20BE400F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,10 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
   <si>
-    <t>hp_announcement</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -116,10 +112,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hp_mission</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ミッションテーブル</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -181,10 +173,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hp_patch_note</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>パッチノートテーブル</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -265,6 +253,18 @@
   </si>
   <si>
     <t>contents_ja</t>
+  </si>
+  <si>
+    <t>hp_contents_announcement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp_contents_mission</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp_contents_patch_note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -820,463 +820,463 @@
     <row r="1" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B2" s="7" t="s">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="9"/>
     </row>
     <row r="3" spans="2:5" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>2</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B13" s="7" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E13" s="9"/>
     </row>
     <row r="14" spans="2:5" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>2</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="3"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E20" s="3"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E26" s="9"/>
     </row>
     <row r="27" spans="2:5" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>2</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E30" s="3"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E31" s="3"/>
     </row>
     <row r="32" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E32" s="6"/>
     </row>
     <row r="33" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="34" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E34" s="9"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="15" t="s">
         <v>2</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>50</v>
-      </c>
       <c r="D40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
